--- a/ppc/data/ppc_data.xlsx
+++ b/ppc/data/ppc_data.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12310" tabRatio="625" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12310" tabRatio="625" firstSheet="2" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="생산제품" sheetId="1" r:id="rId1"/>
-    <sheet name="자재" sheetId="2" r:id="rId2"/>
-    <sheet name="공급업체" sheetId="3" r:id="rId3"/>
-    <sheet name="제품별_기준단가" sheetId="4" r:id="rId4"/>
+    <sheet name="제품별_기준단가" sheetId="4" r:id="rId2"/>
+    <sheet name="자재" sheetId="2" r:id="rId3"/>
+    <sheet name="공급업체" sheetId="3" r:id="rId4"/>
     <sheet name="제품별_자재" sheetId="5" r:id="rId5"/>
     <sheet name="업체별_자재단가" sheetId="6" r:id="rId6"/>
     <sheet name="발주권한자" sheetId="7" r:id="rId7"/>
@@ -24,13 +24,14 @@
     <sheet name="주의사항" sheetId="10" r:id="rId10"/>
     <sheet name="지연시간" sheetId="14" r:id="rId11"/>
     <sheet name="생산주문예" sheetId="12" r:id="rId12"/>
+    <sheet name="정비사" sheetId="15" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">공급업체!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">공급업체!$A$1:$H$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">발주권한자!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">생산제품!$A$1:$E$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">생산주문예!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">자재!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">자재!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">제품별_자재!$A$1:$C$31</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="463">
   <si>
     <t>제품코드</t>
   </si>
@@ -1323,6 +1324,152 @@
   </si>
   <si>
     <t>3개월</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정비팀장</t>
+  </si>
+  <si>
+    <t>경력 15년</t>
+  </si>
+  <si>
+    <t>선임정비사</t>
+  </si>
+  <si>
+    <t>경력 11년</t>
+  </si>
+  <si>
+    <t>경력 9년</t>
+  </si>
+  <si>
+    <t>정비사</t>
+  </si>
+  <si>
+    <t>경력 7년</t>
+  </si>
+  <si>
+    <t>경력 6년</t>
+  </si>
+  <si>
+    <t>주임정비사</t>
+  </si>
+  <si>
+    <t>경력 5년</t>
+  </si>
+  <si>
+    <t>김도현</t>
+  </si>
+  <si>
+    <t>경력 4년</t>
+  </si>
+  <si>
+    <t>서준혁</t>
+  </si>
+  <si>
+    <t>한지훈</t>
+  </si>
+  <si>
+    <t>경력 3년</t>
+  </si>
+  <si>
+    <t>오현석</t>
+  </si>
+  <si>
+    <t>경력 2년</t>
+  </si>
+  <si>
+    <t>정비사 ID</t>
+  </si>
+  <si>
+    <t>경력</t>
+  </si>
+  <si>
+    <t>연락처</t>
+  </si>
+  <si>
+    <t>주 담당 부품</t>
+  </si>
+  <si>
+    <t>부 담당 부품</t>
+  </si>
+  <si>
+    <t>B-001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-005</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-007</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-009</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-2251-2102</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-5872-4501</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-1131-2354</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-5121-1128</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-7754-3547</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-3571-2155</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-2021-0707</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-3900-2028</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-5541-1354</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-1251-1001</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1373,7 +1520,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1381,11 +1528,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E1F2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1405,6 +1561,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2824,7 +2986,636 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="3" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.9140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="7">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7">
+        <v>380000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="7">
+        <v>3500000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="7">
+        <v>4200000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="7">
+        <v>3800000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="7">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="7">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="7">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1600000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="7">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="7">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="7">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="7">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="7">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="7">
+        <v>4800000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="7">
+        <v>3600000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="7">
+        <v>4300000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="7">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="7">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="7">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="7">
+        <v>2700000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="7">
+        <v>360000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="7">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="7">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>230000</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -3048,7 +3839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -4633,363 +5424,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H26"/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="7">
-        <v>180000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="7">
-        <v>220000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="7">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="7">
-        <v>380000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="7">
-        <v>320000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="7">
-        <v>3500000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="7">
-        <v>4200000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2800000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="7">
-        <v>3800000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="7">
-        <v>420000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="7">
-        <v>320000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="7">
-        <v>220000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1600000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1400000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="7">
-        <v>180000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="7">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="7">
-        <v>550000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="7">
-        <v>320000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="7">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="7">
-        <v>4800000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="7">
-        <v>3600000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="7">
-        <v>4300000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="7">
-        <v>4000000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="7">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="7">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="7">
-        <v>2700000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="7">
-        <v>360000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="7">
-        <v>420000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="7">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31">
-        <v>230000</v>
-      </c>
-    </row>
-  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
